--- a/model2/chlb.xlsx
+++ b/model2/chlb.xlsx
@@ -1,39 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\data files of project\chlb2\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBEA3E5-52AF-481C-99BA-6F57CFBB5BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{BA832EA3-F959-4B7A-990D-9BBF42FCC0DF}"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
@@ -41,284 +19,282 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
-    <t>solution num</t>
-  </si>
-  <si>
-    <t>Sample Con</t>
-  </si>
-  <si>
-    <t>No. 1</t>
-  </si>
-  <si>
-    <t>No. 2</t>
-  </si>
-  <si>
-    <t>No. 3</t>
-  </si>
-  <si>
-    <t>No. 4</t>
-  </si>
-  <si>
-    <t>No. 5</t>
-  </si>
-  <si>
-    <t>No. 6</t>
-  </si>
-  <si>
-    <t>No. 7</t>
-  </si>
-  <si>
-    <t>No. 8</t>
-  </si>
-  <si>
-    <t>No. 9</t>
-  </si>
-  <si>
-    <t>No. 10</t>
-  </si>
-  <si>
-    <t>No. 11</t>
-  </si>
-  <si>
-    <t>No. 12</t>
-  </si>
-  <si>
-    <t>No. 13</t>
-  </si>
-  <si>
-    <t>No. 14</t>
-  </si>
-  <si>
-    <t>No. 15</t>
-  </si>
-  <si>
-    <t>No. 16</t>
-  </si>
-  <si>
-    <t>No. 17</t>
-  </si>
-  <si>
-    <t>No. 18</t>
-  </si>
-  <si>
-    <t>No. 19</t>
-  </si>
-  <si>
-    <t>No. 20</t>
-  </si>
-  <si>
-    <t>No. 21</t>
-  </si>
-  <si>
-    <t>No. 22</t>
-  </si>
-  <si>
-    <t>No. 23</t>
-  </si>
-  <si>
-    <t>No. 24</t>
-  </si>
-  <si>
-    <t>No. 25</t>
-  </si>
-  <si>
-    <t>No. 26</t>
-  </si>
-  <si>
-    <t>No. 27</t>
-  </si>
-  <si>
-    <t>No. 28</t>
-  </si>
-  <si>
-    <t>No. 29</t>
-  </si>
-  <si>
-    <t>No. 30</t>
-  </si>
-  <si>
-    <t>No. 31</t>
-  </si>
-  <si>
-    <t>No. 32</t>
-  </si>
-  <si>
-    <t>No. 33</t>
-  </si>
-  <si>
-    <t>No. 34</t>
-  </si>
-  <si>
-    <t>No. 35</t>
-  </si>
-  <si>
-    <t>No. 36</t>
-  </si>
-  <si>
-    <t>No. 37</t>
-  </si>
-  <si>
-    <t>No. 38</t>
-  </si>
-  <si>
-    <t>No. 39</t>
-  </si>
-  <si>
-    <t>No. 40</t>
-  </si>
-  <si>
-    <t>No. 41</t>
-  </si>
-  <si>
-    <t>No. 42</t>
-  </si>
-  <si>
-    <t>No. 43</t>
-  </si>
-  <si>
-    <t>No. 44</t>
-  </si>
-  <si>
-    <t>No. 45</t>
-  </si>
-  <si>
-    <t>No. 46</t>
-  </si>
-  <si>
-    <t>No. 47</t>
-  </si>
-  <si>
-    <t>No. 48</t>
-  </si>
-  <si>
-    <t>No. 49</t>
-  </si>
-  <si>
-    <t>No. 50</t>
-  </si>
-  <si>
-    <t>No. 51</t>
-  </si>
-  <si>
-    <t>No. 52</t>
-  </si>
-  <si>
-    <t>No. 53</t>
-  </si>
-  <si>
-    <t>No. 54</t>
-  </si>
-  <si>
-    <t>No. 55</t>
-  </si>
-  <si>
-    <t>No. 56</t>
-  </si>
-  <si>
-    <t>No. 57</t>
-  </si>
-  <si>
-    <t>No. 58</t>
-  </si>
-  <si>
-    <t>No. 59</t>
-  </si>
-  <si>
-    <t>No. 60</t>
-  </si>
-  <si>
-    <t>No. 61</t>
-  </si>
-  <si>
-    <t>No. 62</t>
-  </si>
-  <si>
-    <t>No. 63</t>
-  </si>
-  <si>
-    <t>No. 64</t>
-  </si>
-  <si>
-    <t>No. 65</t>
-  </si>
-  <si>
-    <t>No. 66</t>
-  </si>
-  <si>
-    <t>No. 67</t>
-  </si>
-  <si>
-    <t>No. 68</t>
-  </si>
-  <si>
-    <t>No. 69</t>
-  </si>
-  <si>
-    <t>No. 70</t>
-  </si>
-  <si>
-    <t>No. 71</t>
-  </si>
-  <si>
-    <t>No. 72</t>
-  </si>
-  <si>
-    <t>No. 73</t>
-  </si>
-  <si>
-    <t>No. 74</t>
-  </si>
-  <si>
-    <t>No. 75</t>
-  </si>
-  <si>
-    <t>No. 76</t>
-  </si>
-  <si>
-    <t>No. 77</t>
-  </si>
-  <si>
-    <t>No. 78</t>
-  </si>
-  <si>
-    <t>No. 79</t>
-  </si>
-  <si>
-    <t>No. 80</t>
-  </si>
-  <si>
-    <t>No. 81</t>
-  </si>
-  <si>
-    <t>No. 82</t>
-  </si>
-  <si>
-    <t>No. 83</t>
-  </si>
-  <si>
-    <t>integration time(mS)</t>
-  </si>
-  <si>
     <t>chlb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">solution num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample Con</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integration time(mS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. 83</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.000000"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -330,18 +306,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor indexed="5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
@@ -356,19 +331,44 @@
       <bottom style="medium">
         <color rgb="FFCCCCCC"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="7">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -386,8 +386,291 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -429,108 +712,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Aptos Display"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Aptos Narrow"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -538,7 +727,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -564,7 +753,7 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -641,7 +830,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -673,7 +862,7 @@
   </a:themeElements>
   <a:objectDefaults>
     <a:lnDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -692,44 +881,38 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EE7187B-D010-4AF3-8954-A82031EBE072}">
-  <dimension ref="A1:D85"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="16.36328125" customWidth="1"/>
+    <col customWidth="1" min="2" max="2" width="15.50390625"/>
+    <col customWidth="1" min="3" max="3" width="16.36328125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>10.485431999999998</v>
@@ -738,9 +921,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>9.8300924999999975</v>
@@ -749,9 +932,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>9.2518517647058793</v>
@@ -760,9 +943,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>8.7378599999999977</v>
@@ -771,9 +954,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>8.2779726315789457</v>
@@ -782,9 +965,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>7.8640739999999978</v>
@@ -793,9 +976,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <v>7.4708702999999987</v>
@@ -804,9 +987,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>7.0973267849999981</v>
@@ -815,9 +998,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B11">
         <v>6.7424604457499981</v>
@@ -826,9 +1009,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <v>6.4053374234624982</v>
@@ -837,9 +1020,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>6.0850705522893733</v>
@@ -848,9 +1031,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>5.7808170246749047</v>
@@ -859,9 +1042,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15">
         <v>5.491776173441159</v>
@@ -870,9 +1053,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>5.2171873647691012</v>
@@ -881,9 +1064,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17">
       <c r="A17" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B17">
         <v>4.9563279965306464</v>
@@ -892,9 +1075,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B18">
         <v>4.7085115967041142</v>
@@ -903,9 +1086,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19">
       <c r="A19" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B19">
         <v>4.4730860168689084</v>
@@ -914,9 +1097,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20">
       <c r="A20" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B20">
         <v>4.2494317160254633</v>
@@ -925,9 +1108,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>4.0369601302241902</v>
@@ -936,9 +1119,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22">
       <c r="A22" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B22">
         <v>3.8351121237129808</v>
@@ -947,9 +1130,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23">
       <c r="A23" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B23">
         <v>3.6433565175273315</v>
@@ -958,9 +1141,9 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24">
       <c r="A24" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B24">
         <v>3.4611886916509649</v>
@@ -969,9 +1152,9 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25">
       <c r="A25" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B25">
         <v>3.2881292570684169</v>
@@ -980,9 +1163,9 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26">
       <c r="A26" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B26">
         <v>3.1237227942149959</v>
@@ -991,9 +1174,9 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27">
       <c r="A27" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B27">
         <v>2.9675366545042463</v>
@@ -1002,9 +1185,9 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28">
       <c r="A28" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B28">
         <v>2.8191598217790341</v>
@@ -1013,9 +1196,9 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29">
       <c r="A29" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B29">
         <v>2.6782018306900826</v>
@@ -1024,9 +1207,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30">
       <c r="A30" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B30">
         <v>2.5442917391555784</v>
@@ -1035,9 +1218,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31">
       <c r="A31" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B31">
         <v>2.4170771521977992</v>
@@ -1046,9 +1229,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32">
       <c r="A32" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B32">
         <v>2.2962232945879091</v>
@@ -1057,9 +1240,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33">
       <c r="A33" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B33">
         <v>2.1814121298585136</v>
@@ -1068,9 +1251,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34">
       <c r="A34" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B34">
         <v>2.072341523365588</v>
@@ -1079,9 +1262,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35">
       <c r="A35" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B35">
         <v>1.9687244471973084</v>
@@ -1090,9 +1273,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36">
       <c r="A36" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B36">
         <v>1.8702882248374428</v>
@@ -1101,9 +1284,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37">
       <c r="A37" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B37">
         <v>1.7767738135955706</v>
@@ -1112,9 +1295,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38">
       <c r="A38" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B38">
         <v>1.6879351229157922</v>
@@ -1123,9 +1306,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39">
       <c r="A39" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B39">
         <v>1.6035383667700025</v>
@@ -1134,9 +1317,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40">
       <c r="A40" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B40">
         <v>1.5233614484315023</v>
@@ -1145,9 +1328,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41">
       <c r="A41" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B41">
         <v>1.4471933760099271</v>
@@ -1156,9 +1339,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42">
       <c r="A42" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B42">
         <v>1.3748337072094308</v>
@@ -1167,9 +1350,9 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" ht="15">
       <c r="A43" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B43">
         <v>1.3060920218489591</v>
@@ -1178,9 +1361,9 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" ht="15">
       <c r="A44" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B44" s="3">
         <v>1.897</v>
@@ -1189,9 +1372,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" ht="15">
       <c r="A45" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B45" s="3">
         <v>1.518</v>
@@ -1200,9 +1383,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" ht="15">
       <c r="A46" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B46" s="3">
         <v>1.2649999999999999</v>
@@ -1211,9 +1394,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" ht="15">
       <c r="A47" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B47" s="3">
         <v>1.0840000000000001</v>
@@ -1222,9 +1405,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" ht="15">
       <c r="A48" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B48" s="3">
         <v>0.94799999999999995</v>
@@ -1233,9 +1416,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" ht="15">
       <c r="A49" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B49" s="3">
         <v>0.84299999999999997</v>
@@ -1244,9 +1427,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" ht="15">
       <c r="A50" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B50" s="3">
         <v>0.749</v>
@@ -1255,9 +1438,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" ht="15">
       <c r="A51" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B51" s="3">
         <v>0.66600000000000004</v>
@@ -1266,9 +1449,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" ht="15">
       <c r="A52" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B52" s="3">
         <v>0.59199999999999997</v>
@@ -1277,9 +1460,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" ht="15">
       <c r="A53" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B53" s="3">
         <v>0.49299999999999999</v>
@@ -1288,9 +1471,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" ht="15">
       <c r="A54" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B54" s="3">
         <v>0.41099999999999998</v>
@@ -1299,9 +1482,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" ht="15">
       <c r="A55" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B55" s="3">
         <v>0.32900000000000001</v>
@@ -1310,20 +1493,20 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56">
       <c r="A56" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B56">
-        <v>1.64</v>
+        <v>1.6399999999999999</v>
       </c>
       <c r="C56">
         <v>3000</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57">
       <c r="A57" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B57">
         <v>1.1299999999999999</v>
@@ -1332,20 +1515,20 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58">
       <c r="A58" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B58">
-        <v>1.41</v>
+        <v>1.4099999999999999</v>
       </c>
       <c r="C58">
         <v>3000</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59">
       <c r="A59" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B59">
         <v>1.1100000000000001</v>
@@ -1354,9 +1537,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60">
       <c r="A60" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B60">
         <v>1.74</v>
@@ -1365,9 +1548,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61">
       <c r="A61" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B61">
         <v>1.55</v>
@@ -1376,9 +1559,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62">
       <c r="A62" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B62">
         <v>2.04</v>
@@ -1387,31 +1570,31 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63">
       <c r="A63" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B63">
-        <v>1.88</v>
+        <v>1.8799999999999999</v>
       </c>
       <c r="C63">
         <v>3000</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64">
       <c r="A64" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B64">
-        <v>1.41</v>
+        <v>1.4099999999999999</v>
       </c>
       <c r="C64">
         <v>3000</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65">
       <c r="A65" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B65">
         <v>1.48</v>
@@ -1420,20 +1603,20 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66">
       <c r="A66" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B66">
-        <v>1.56</v>
+        <v>1.5600000000000001</v>
       </c>
       <c r="C66">
         <v>3000</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67">
       <c r="A67" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B67">
         <v>2.4900000000000002</v>
@@ -1442,20 +1625,20 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68">
       <c r="A68" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B68">
-        <v>1.88</v>
+        <v>1.8799999999999999</v>
       </c>
       <c r="C68">
         <v>3000</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69">
       <c r="A69" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B69">
         <v>1.74</v>
@@ -1464,31 +1647,31 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70">
       <c r="A70" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B70">
-        <v>1.92</v>
+        <v>1.9199999999999999</v>
       </c>
       <c r="C70">
         <v>3000</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71">
       <c r="A71" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B71">
-        <v>1.88</v>
+        <v>1.8799999999999999</v>
       </c>
       <c r="C71">
         <v>3000</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72">
       <c r="A72" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B72">
         <v>1.5</v>
@@ -1497,9 +1680,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73">
       <c r="A73" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B73">
         <v>1.7</v>
@@ -1508,64 +1691,64 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74">
       <c r="A74" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B74">
-        <v>1.81</v>
+        <v>1.8100000000000001</v>
       </c>
       <c r="C74">
         <v>3000</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75">
       <c r="A75" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B75">
-        <v>1.62</v>
+        <v>1.6200000000000001</v>
       </c>
       <c r="C75">
         <v>3000</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76">
       <c r="A76" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B76">
-        <v>1.94</v>
+        <v>1.9399999999999999</v>
       </c>
       <c r="C76">
         <v>3000</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77">
       <c r="A77" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B77">
-        <v>1.6</v>
+        <v>1.6000000000000001</v>
       </c>
       <c r="C77">
         <v>3000</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78">
       <c r="A78" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B78">
-        <v>1.31</v>
+        <v>1.3100000000000001</v>
       </c>
       <c r="C78">
         <v>3000</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79">
       <c r="A79" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B79">
         <v>1.48</v>
@@ -1574,20 +1757,20 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80">
       <c r="A80" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B80">
-        <v>1.34</v>
+        <v>1.3400000000000001</v>
       </c>
       <c r="C80">
         <v>3000</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81">
       <c r="A81" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B81">
         <v>1.21</v>
@@ -1596,27 +1779,950 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="82">
       <c r="A82" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4">
+        <v>10.485431999999998</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4">
+        <v>9.8300924999999975</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4">
+        <v>9.2518517647058793</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="4">
+        <v>8.7378599999999977</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4">
+        <v>8.2779726315789457</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="4">
+        <v>7.8640739999999978</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="4">
+        <v>7.4708702999999987</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="4">
+        <v>7.0973267849999981</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="4">
+        <v>6.7424604457499981</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="4">
+        <v>6.4053374234624982</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="4">
+        <v>6.0850705522893733</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="4">
+        <v>5.7808170246749047</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="4">
+        <v>5.491776173441159</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="4">
+        <v>5.2171873647691012</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="4">
+        <v>4.9563279965306464</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="4">
+        <v>4.7085115967041142</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="4">
+        <v>4.4730860168689084</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="4">
+        <v>4.2494317160254633</v>
+      </c>
+      <c r="C19" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="4">
+        <v>4.0369601302241902</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="4">
+        <v>3.8351121237129808</v>
+      </c>
+      <c r="C21" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="4">
+        <v>3.6433565175273315</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="4">
+        <v>3.4611886916509649</v>
+      </c>
+      <c r="C23" s="4">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="4">
+        <v>3.2881292570684169</v>
+      </c>
+      <c r="C24" s="4">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="4">
+        <v>3.1237227942149959</v>
+      </c>
+      <c r="C25" s="4">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="4">
+        <v>2.9675366545042463</v>
+      </c>
+      <c r="C26" s="4">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="4">
+        <v>2.8191598217790341</v>
+      </c>
+      <c r="C27" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="4">
+        <v>2.6782018306900826</v>
+      </c>
+      <c r="C28" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="4">
+        <v>2.5442917391555784</v>
+      </c>
+      <c r="C29" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="4">
+        <v>2.4170771521977992</v>
+      </c>
+      <c r="C30" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="4">
+        <v>2.2962232945879091</v>
+      </c>
+      <c r="C31" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="4">
+        <v>2.1814121298585136</v>
+      </c>
+      <c r="C32" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="4">
+        <v>2.072341523365588</v>
+      </c>
+      <c r="C33" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="4">
+        <v>1.9687244471973084</v>
+      </c>
+      <c r="C34" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="4">
+        <v>1.8702882248374428</v>
+      </c>
+      <c r="C35" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="4">
+        <v>1.7767738135955706</v>
+      </c>
+      <c r="C36" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="4">
+        <v>1.6879351229157922</v>
+      </c>
+      <c r="C37" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="4">
+        <v>1.6035383667700025</v>
+      </c>
+      <c r="C38" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="4">
+        <v>1.5233614484315023</v>
+      </c>
+      <c r="C39" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="4">
+        <v>1.4471933760099271</v>
+      </c>
+      <c r="C40" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="4">
+        <v>1.3748337072094308</v>
+      </c>
+      <c r="C41" s="4">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="5">
+        <v>1.3060920218489591</v>
+      </c>
+      <c r="C42" s="4">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="3">
+        <v>1.897</v>
+      </c>
+      <c r="C43" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44" s="3">
+        <v>1.518</v>
+      </c>
+      <c r="C44" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="3">
+        <v>1.2649999999999999</v>
+      </c>
+      <c r="C45" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="3">
+        <v>1.0840000000000001</v>
+      </c>
+      <c r="C46" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="3">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="C47" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48" s="3">
+        <v>0.84299999999999997</v>
+      </c>
+      <c r="C48" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" s="3">
+        <v>0.749</v>
+      </c>
+      <c r="C49" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" s="3">
+        <v>0.66600000000000004</v>
+      </c>
+      <c r="C50" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51" s="3">
+        <v>0.59199999999999997</v>
+      </c>
+      <c r="C51" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="3">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="C52" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" s="3">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="C53" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="3">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="C54" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" s="4">
+        <v>1.6399999999999999</v>
+      </c>
+      <c r="C55" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" s="4">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C56" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" s="4">
+        <v>1.4099999999999999</v>
+      </c>
+      <c r="C57" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B58" s="4">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="C58" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B59" s="4">
+        <v>1.74</v>
+      </c>
+      <c r="C59" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B60" s="4">
+        <v>1.55</v>
+      </c>
+      <c r="C60" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B61" s="4">
+        <v>2.04</v>
+      </c>
+      <c r="C61" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B62" s="4">
+        <v>1.8799999999999999</v>
+      </c>
+      <c r="C62" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B63" s="4">
+        <v>1.4099999999999999</v>
+      </c>
+      <c r="C63" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B64" s="4">
+        <v>1.48</v>
+      </c>
+      <c r="C64" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B65" s="4">
+        <v>1.5600000000000001</v>
+      </c>
+      <c r="C65" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B66" s="4">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="C66" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B67" s="4">
+        <v>1.8799999999999999</v>
+      </c>
+      <c r="C67" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B68" s="4">
+        <v>1.74</v>
+      </c>
+      <c r="C68" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B69" s="4">
+        <v>1.9199999999999999</v>
+      </c>
+      <c r="C69" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B70" s="4">
+        <v>1.8799999999999999</v>
+      </c>
+      <c r="C70" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B71" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="C71" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B72" s="4">
+        <v>1.7</v>
+      </c>
+      <c r="C72" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B73" s="4">
+        <v>1.8100000000000001</v>
+      </c>
+      <c r="C73" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B74" s="4">
+        <v>1.6200000000000001</v>
+      </c>
+      <c r="C74" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B75" s="4">
+        <v>1.9399999999999999</v>
+      </c>
+      <c r="C75" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B76" s="4">
+        <v>1.6000000000000001</v>
+      </c>
+      <c r="C76" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B77" s="4">
+        <v>1.3100000000000001</v>
+      </c>
+      <c r="C77" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B78" s="4">
+        <v>1.48</v>
+      </c>
+      <c r="C78" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B79" s="4">
+        <v>1.3400000000000001</v>
+      </c>
+      <c r="C79" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B80" s="4">
+        <v>1.21</v>
+      </c>
+      <c r="C80" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+    </row>
+    <row r="83">
       <c r="A83" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+    </row>
+    <row r="84">
       <c r="A84" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A85" s="2" t="s">
-        <v>84</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>